--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:56</t>
+    <t xml:space="preserve">2026-09-10 01:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:07</t>
+    <t xml:space="preserve">2026-09-12 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -111,6 +111,9 @@
     <t xml:space="preserve">Rancagua</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Requínoa</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:19</t>
+    <t xml:space="preserve">2026-09-23 23:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6310</v>
+        <v>6204</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>55.21</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>54.94</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6114</v>
+        <v>6306</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>54.68</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6308</v>
+        <v>6114</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.34</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6102</v>
+        <v>6308</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>53.27</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6201</v>
+        <v>6102</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>52.81</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6116</v>
+        <v>6201</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>52.02</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6116</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>52.02</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:48</t>
+    <t xml:space="preserve">2026-10-02 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:30</t>
+    <t xml:space="preserve">2026-10-04 10:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:27</t>
+    <t xml:space="preserve">2026-10-05 15:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
